--- a/Pruebas calificadas/COLEGIO CIUDAD DE MONTREAL_901_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO CIUDAD DE MONTREAL_901_CALIFICADO.xlsx
@@ -1444,9 +1444,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -2962,9 +2962,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB10" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -3199,9 +3199,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB11" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -3705,9 +3705,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB13" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -4199,9 +4199,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB15" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -4452,9 +4452,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB16" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -4705,9 +4705,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB17" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -4958,9 +4958,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB18" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -5211,9 +5211,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB19" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -5464,9 +5464,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB20" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -5934,9 +5934,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB22" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -6187,9 +6187,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB23" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -6440,9 +6440,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB24" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -6693,9 +6693,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB25" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -7452,9 +7452,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB28" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO CIUDAD DE MONTREAL_901_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO CIUDAD DE MONTREAL_901_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -3068,11 +3032,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -3321,11 +3281,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -3574,11 +3530,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -3827,11 +3779,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -4068,11 +4016,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -4321,11 +4265,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -4574,11 +4514,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -4827,11 +4763,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -5080,11 +5012,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -5333,11 +5261,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -5586,11 +5510,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -5803,11 +5723,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -6056,11 +5972,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -6309,11 +6221,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -6562,11 +6470,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -6815,11 +6719,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -7068,11 +6968,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -7321,11 +7217,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -7574,11 +7466,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -7827,11 +7715,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -8080,11 +7964,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -8325,11 +8205,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -8578,11 +8454,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -8831,11 +8703,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -9084,11 +8952,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -9337,11 +9201,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -9590,11 +9450,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -9843,11 +9699,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -10096,11 +9948,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -10349,11 +10197,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -10602,11 +10446,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -10855,11 +10695,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -11100,11 +10936,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -11353,11 +11185,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -11594,11 +11422,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -11847,11 +11671,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -12100,11 +11920,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -12353,11 +12169,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -12590,11 +12402,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -12843,11 +12651,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -13096,11 +12900,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -13349,11 +13149,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -13602,11 +13398,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -13855,11 +13647,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -14108,11 +13896,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -14361,11 +14145,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -14614,11 +14394,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -14867,11 +14643,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
@@ -15120,11 +14892,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001028266</t>
